--- a/business_forms/045_partner_commission_program_application_form--business_forms.xlsx
+++ b/business_forms/045_partner_commission_program_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Application Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Partner Information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter your email address</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contact Information</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,20 +606,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Application Information</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How did you hear about us?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide how you heard about our program</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +633,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Partner Type</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select your partner type</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +660,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Agreement</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Submission</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select your submission preferences</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +687,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Workdays</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select your available workdays</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +714,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Attachments</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Agreement</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select the terms of your agreement</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,10 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Attachments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Attach any supporting documents</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,7 +758,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,10 +768,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Agreement Terms</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select the terms of your agreement</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,7 +785,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,13 +795,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Terms and Conditions</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Read and agree to the terms and conditions</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -783,75 +827,6 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -896,238 +871,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>partner_type</t>
+          <t>business_partner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Partner Type</t>
+          <t>Business Partner</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>form_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>business_partner</t>
+          <t>individual_partner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Business Partner</t>
+          <t>Individual Partner</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>individual_partner</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Individual Partner</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>form_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_11_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>am</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>form_8_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>pm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>PM</t>
         </is>
       </c>
     </row>
@@ -1139,199 +1114,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>form_12_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>weekdays</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weekdays</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>form_13_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>weekends</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Weekends</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>monday</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tuesday</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>wednesday</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>thursday</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>friday</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>saturday</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>form_14_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sunday</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>form_15_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>am</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>form_15_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pm</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PM</t>
+          <t>No</t>
         </is>
       </c>
     </row>
